--- a/reports/Selenium_Test_Results.xlsx
+++ b/reports/Selenium_Test_Results.xlsx
@@ -38,14 +38,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF0000"/>
-        <bgColor rgb="00FF0000"/>
+        <fgColor rgb="0000FF00"/>
+        <bgColor rgb="0000FF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000FF00"/>
-        <bgColor rgb="0000FF00"/>
+        <fgColor rgb="00FF0000"/>
+        <bgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -445,15 +445,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="882" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -473,35 +472,35 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Execution Date: 2026-06-14 10:20:08</t>
+          <t>Execution Date: 2026-06-18 17:40:38</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Total Tests: 3</t>
+          <t>Total Tests: 58</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Passed: 1</t>
+          <t>Passed: 53</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Failed: 2</t>
+          <t>Failed: 5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Pass Percentage: 33.33%</t>
+          <t>Pass Percentage: 91.38%</t>
         </is>
       </c>
     </row>
@@ -518,20 +517,15 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Execution Time</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Execution Time (s)</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -540,88 +534,1488 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>TC_REGISTRATION_001</t>
+          <t>TC_NAVIGATION_001</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Valid Registration</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Test_Registration</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>12.61</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>selenium.common.exceptions.TimeoutException: Message:</t>
+          <t>Unauthenticated Navigation</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>TC_REGISTRATION_002</t>
+          <t>TC_NAVIGATION_002</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Registration Existing User</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Test_Registration</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>selenium.common.exceptions.TimeoutException: Message:</t>
+          <t>Navigation Links</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>TC_REGISTRATION_003</t>
+          <t>TC_LOGIN_003</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t>Valid Login</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>TC_LOGIN_004</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Invalid Password</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>15.61</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>TC_LOGIN_005</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Invalid Username</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>TC_LOGIN_006</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Login Empty Fields</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>TC_LOGIN_007</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Valid Login</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>16.56</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>TC_LOGIN_008</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Invalid Password</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>TC_LOGIN_009</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Invalid Username</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>TC_LOGIN_010</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Login Empty Fields</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>TC_LOGIN_011</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Provided Credentials</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>TC_LOGOUT_012</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Logout</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>TC_SETTINGS_013</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Model Telemetry Loads</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>TC_E2E_014</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Full E2E Flow</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>TC_NAVIGATION_015</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Unauthenticated Navigation</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TC_NAVIGATION_016</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Navigation Links</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>TC_SETTINGS_017</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Model Telemetry Loads</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TC_DASHBOARD_018</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Dashboard Loads</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>selenium.common.exceptions.NoSuchElementException: Message: no such element: Unable to locate element: {"method":"xpath","selector":"//input[@placeholder='Enter username']"}
+  (Session info: chrome=149.0.7827.114); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+#0 0x5624da87380a &lt;unknown&gt;
+#1 0x5624da256289 &lt;unknown&gt;
+#2 0x5624da2aa9b4 &lt;unknown&gt;
+#3 0x5624da2aac01 &lt;unknown&gt;
+#4 0x5624da2f5874 &lt;unknown&gt;
+#5 0x5624da2f2a4c &lt;unknown&gt;
+#6 0x5624da29df7f &lt;unknown&gt;
+#7 0x5624da29ed61 &lt;unknown&gt;
+#8 0x5624da83a0f7 &lt;unknown&gt;
+#9 0x5624da8388bd &lt;unknown&gt;
+#10 0x5624da8235a6 &lt;unknown&gt;
+#11 0x5624da83949a &lt;unknown&gt;
+#12 0x5624da80b560 &lt;unknown&gt;
+#13 0x5624da860288 &lt;unknown&gt;
+#14 0x5624da860425 &lt;unknown&gt;
+#15 0x5624da87238e &lt;unknown&gt;
+#16 0x7f419d69caa4 &lt;unknown&gt;
+#17 0x7f419d729c6c &lt;unknown&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>TC_DASHBOARD_019</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>User Profile Display</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TC_DASHBOARD_020</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Dashboard Stats Exist</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>TC_DASHBOARD_021</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Retrain Model Button</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>TC_DASHBOARD_022</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Dashboard Loads</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>TC_DASHBOARD_023</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>User Profile Display</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>TC_DASHBOARD_024</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Dashboard Stats Exist</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>TC_DASHBOARD_025</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Analytics Charts Rendering</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TC_DASHBOARD_026</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Retrain Model Button</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>TC_PROFILE_027</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Profile Loads</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TC_PROFILE_028</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Edit Profile</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>TC_PROFILE_029</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Profile Loads</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TC_PROFILE_030</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Edit Profile</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>TC_PREDICTION_031</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Transmit Metrics Success</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>TC_PREDICTION_032</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Cognitive Strain Prediction</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>TC_PREDICTION_033</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Behavioral Drift Score</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TC_NOTIFICATIONS_034</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Notification Bell Presence</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>TC_NOTIFICATIONS_035</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Medium Strain Notification Generation</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TC_NOTIFICATIONS_036</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Notifications History Page</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>TC_NOTIFICATIONS_037</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Delete Notification</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>TC_REGISTRATION_038</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Valid Registration</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>TC_REGISTRATION_039</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Registration Existing User</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TC_REGISTRATION_040</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
           <t>Registration Empty Fields</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Test_Registration</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>TC_RESPONSIVE_041</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Responsive Layout</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>TC_ROUTING_042</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Protected Route Redirect</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>TC_ROUTING_043</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Unknown Route Redirect</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>selenium.common.exceptions.TimeoutException: Message:</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>TC_NOTIFICATIONS_044</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Notification Bell Presence</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>TC_NOTIFICATIONS_045</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Medium Strain Notification Generation</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>TC_NOTIFICATIONS_046</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Notifications History Page</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>TC_NOTIFICATIONS_047</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Delete Notification</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>TC_PREDICTION_048</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Transmit Metrics Success</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>TC_PREDICTION_049</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Cognitive Strain Prediction</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>TC_PREDICTION_050</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Behavioral Drift Score</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>TC_E2E_051</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Full E2E Flow</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>selenium.common.exceptions.NoSuchElementException: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="fullName"]"}
+  (Session info: chrome=149.0.7827.114); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+#0 0x55b2bc18480a &lt;unknown&gt;
+#1 0x55b2bbb67289 &lt;unknown&gt;
+#2 0x55b2bbbbb9b4 &lt;unknown&gt;
+#3 0x55b2bbbbbc01 &lt;unknown&gt;
+#4 0x55b2bbc06874 &lt;unknown&gt;
+#5 0x55b2bbc03a4c &lt;unknown&gt;
+#6 0x55b2bbbaef7f &lt;unknown&gt;
+#7 0x55b2bbbafd61 &lt;unknown&gt;
+#8 0x55b2bc14b0f7 &lt;unknown&gt;
+#9 0x55b2bc1498bd &lt;unknown&gt;
+#10 0x55b2bc1345a6 &lt;unknown&gt;
+#11 0x55b2bc14a49a &lt;unknown&gt;
+#12 0x55b2bc11c560 &lt;unknown&gt;
+#13 0x55b2bc171288 &lt;unknown&gt;
+#14 0x55b2bc171425 &lt;unknown&gt;
+#15 0x55b2bc18338e &lt;unknown&gt;
+#16 0x7f4c8a69caa4 &lt;unknown&gt;
+#17 0x7f4c8a729c6c &lt;unknown&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>TC_REGISTRATION_052</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Valid Registration</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>selenium.common.exceptions.TimeoutException: Message:</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>TC_REGISTRATION_053</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Registration Existing User</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>selenium.common.exceptions.TimeoutException: Message:</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>TC_REGISTRATION_054</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Registration Empty Fields</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
         <v>1.79</v>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>TC_LOGOUT_055</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Logout</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>TC_ROUTING_056</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Protected Route Redirect</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>TC_ROUTING_057</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Unknown Route Redirect</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>TC_RESPONSIVE_058</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Responsive Layout</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>Executed Successfully</t>
         </is>

--- a/reports/Selenium_Test_Results.xlsx
+++ b/reports/Selenium_Test_Results.xlsx
@@ -38,14 +38,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF0000"/>
-        <bgColor rgb="00FF0000"/>
+        <fgColor rgb="0000FF00"/>
+        <bgColor rgb="0000FF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000FF00"/>
-        <bgColor rgb="0000FF00"/>
+        <fgColor rgb="00FF0000"/>
+        <bgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -445,15 +445,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="882" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -473,35 +472,35 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Execution Date: 2026-06-14 10:20:08</t>
+          <t>Execution Date: 2026-06-18 17:49:38</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Total Tests: 3</t>
+          <t>Total Tests: 58</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Passed: 1</t>
+          <t>Passed: 53</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Failed: 2</t>
+          <t>Failed: 5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Pass Percentage: 33.33%</t>
+          <t>Pass Percentage: 91.38%</t>
         </is>
       </c>
     </row>
@@ -518,20 +517,15 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Execution Time</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Execution Time (s)</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -540,88 +534,1488 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>TC_REGISTRATION_001</t>
+          <t>TC_NAVIGATION_001</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Valid Registration</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Test_Registration</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>12.61</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>selenium.common.exceptions.TimeoutException: Message:</t>
+          <t>Unauthenticated Navigation</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>TC_REGISTRATION_002</t>
+          <t>TC_NAVIGATION_002</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Registration Existing User</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Test_Registration</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>selenium.common.exceptions.TimeoutException: Message:</t>
+          <t>Navigation Links</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>TC_REGISTRATION_003</t>
+          <t>TC_LOGIN_003</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t>Valid Login</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>TC_LOGIN_004</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Invalid Password</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>15.61</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>TC_LOGIN_005</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Invalid Username</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>TC_LOGIN_006</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Login Empty Fields</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>TC_LOGIN_007</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Valid Login</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>TC_LOGIN_008</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Invalid Password</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>TC_LOGIN_009</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Invalid Username</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>TC_LOGIN_010</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Login Empty Fields</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>12.21</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>TC_LOGIN_011</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Provided Credentials</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>TC_LOGOUT_012</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Logout</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>TC_SETTINGS_013</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Model Telemetry Loads</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>TC_E2E_014</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Full E2E Flow</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>TC_NAVIGATION_015</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Unauthenticated Navigation</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TC_NAVIGATION_016</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Navigation Links</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>TC_SETTINGS_017</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Model Telemetry Loads</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TC_DASHBOARD_018</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Dashboard Loads</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>selenium.common.exceptions.NoSuchElementException: Message: no such element: Unable to locate element: {"method":"xpath","selector":"//input[@placeholder='Enter username']"}
+  (Session info: chrome=149.0.7827.114); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+#0 0x5624da87380a &lt;unknown&gt;
+#1 0x5624da256289 &lt;unknown&gt;
+#2 0x5624da2aa9b4 &lt;unknown&gt;
+#3 0x5624da2aac01 &lt;unknown&gt;
+#4 0x5624da2f5874 &lt;unknown&gt;
+#5 0x5624da2f2a4c &lt;unknown&gt;
+#6 0x5624da29df7f &lt;unknown&gt;
+#7 0x5624da29ed61 &lt;unknown&gt;
+#8 0x5624da83a0f7 &lt;unknown&gt;
+#9 0x5624da8388bd &lt;unknown&gt;
+#10 0x5624da8235a6 &lt;unknown&gt;
+#11 0x5624da83949a &lt;unknown&gt;
+#12 0x5624da80b560 &lt;unknown&gt;
+#13 0x5624da860288 &lt;unknown&gt;
+#14 0x5624da860425 &lt;unknown&gt;
+#15 0x5624da87238e &lt;unknown&gt;
+#16 0x7f419d69caa4 &lt;unknown&gt;
+#17 0x7f419d729c6c &lt;unknown&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>TC_DASHBOARD_019</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>User Profile Display</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TC_DASHBOARD_020</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Dashboard Stats Exist</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>TC_DASHBOARD_021</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Retrain Model Button</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>TC_DASHBOARD_022</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Dashboard Loads</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>TC_DASHBOARD_023</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>User Profile Display</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>TC_DASHBOARD_024</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Dashboard Stats Exist</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>TC_DASHBOARD_025</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Analytics Charts Rendering</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TC_DASHBOARD_026</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Retrain Model Button</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>TC_PROFILE_027</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Profile Loads</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TC_PROFILE_028</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Edit Profile</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>TC_PROFILE_029</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Profile Loads</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TC_PROFILE_030</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Edit Profile</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>TC_PREDICTION_031</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Transmit Metrics Success</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>TC_PREDICTION_032</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Cognitive Strain Prediction</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>TC_PREDICTION_033</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Behavioral Drift Score</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TC_NOTIFICATIONS_034</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Notification Bell Presence</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>TC_NOTIFICATIONS_035</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Medium Strain Notification Generation</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TC_NOTIFICATIONS_036</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Notifications History Page</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>TC_NOTIFICATIONS_037</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Delete Notification</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>TC_REGISTRATION_038</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Valid Registration</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>TC_REGISTRATION_039</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Registration Existing User</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TC_REGISTRATION_040</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
           <t>Registration Empty Fields</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Test_Registration</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>TC_RESPONSIVE_041</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Responsive Layout</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>TC_ROUTING_042</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Protected Route Redirect</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>TC_ROUTING_043</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Unknown Route Redirect</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>selenium.common.exceptions.TimeoutException: Message:</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>TC_NOTIFICATIONS_044</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Notification Bell Presence</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>TC_NOTIFICATIONS_045</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Medium Strain Notification Generation</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>TC_NOTIFICATIONS_046</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Notifications History Page</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>TC_NOTIFICATIONS_047</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Delete Notification</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>TC_PREDICTION_048</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Transmit Metrics Success</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>TC_PREDICTION_049</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Cognitive Strain Prediction</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>TC_PREDICTION_050</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Behavioral Drift Score</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>TC_E2E_051</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Full E2E Flow</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>selenium.common.exceptions.NoSuchElementException: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="fullName"]"}
+  (Session info: chrome=149.0.7827.114); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+#0 0x55b2bc18480a &lt;unknown&gt;
+#1 0x55b2bbb67289 &lt;unknown&gt;
+#2 0x55b2bbbbb9b4 &lt;unknown&gt;
+#3 0x55b2bbbbbc01 &lt;unknown&gt;
+#4 0x55b2bbc06874 &lt;unknown&gt;
+#5 0x55b2bbc03a4c &lt;unknown&gt;
+#6 0x55b2bbbaef7f &lt;unknown&gt;
+#7 0x55b2bbbafd61 &lt;unknown&gt;
+#8 0x55b2bc14b0f7 &lt;unknown&gt;
+#9 0x55b2bc1498bd &lt;unknown&gt;
+#10 0x55b2bc1345a6 &lt;unknown&gt;
+#11 0x55b2bc14a49a &lt;unknown&gt;
+#12 0x55b2bc11c560 &lt;unknown&gt;
+#13 0x55b2bc171288 &lt;unknown&gt;
+#14 0x55b2bc171425 &lt;unknown&gt;
+#15 0x55b2bc18338e &lt;unknown&gt;
+#16 0x7f4c8a69caa4 &lt;unknown&gt;
+#17 0x7f4c8a729c6c &lt;unknown&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>TC_REGISTRATION_052</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Valid Registration</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>selenium.common.exceptions.TimeoutException: Message:</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>TC_REGISTRATION_053</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Registration Existing User</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>selenium.common.exceptions.TimeoutException: Message:</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>TC_REGISTRATION_054</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Registration Empty Fields</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
         <v>1.79</v>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>TC_LOGOUT_055</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Logout</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>TC_ROUTING_056</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Protected Route Redirect</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>TC_ROUTING_057</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Unknown Route Redirect</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Executed Successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>TC_RESPONSIVE_058</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Responsive Layout</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>Executed Successfully</t>
         </is>

--- a/reports/Selenium_Test_Results.xlsx
+++ b/reports/Selenium_Test_Results.xlsx
@@ -472,7 +472,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Execution Date: 2026-06-18 17:40:38</t>
+          <t>Execution Date: 2026-06-18 18:26:51</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>16.56</v>
+        <v>16.53</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>15.67</v>
+        <v>15.7</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>11.43</v>
+        <v>11.47</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>12.23</v>
+        <v>12.25</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>5.93</v>
+        <v>5.92</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>4.04</v>
+        <v>4.09</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>4.32</v>
+        <v>4.31</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>4.25</v>
+        <v>4.28</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>5.05</v>
+        <v>5.2</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>3.13</v>
+        <v>3.07</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>

--- a/reports/Selenium_Test_Results.xlsx
+++ b/reports/Selenium_Test_Results.xlsx
@@ -452,7 +452,7 @@
     <col width="39" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="882" customWidth="1" min="5" max="5"/>
+    <col width="4951" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Execution Date: 2026-06-18 18:26:51</t>
+          <t>Execution Date: 2026-06-18 18:43:29</t>
         </is>
       </c>
     </row>
@@ -486,21 +486,21 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Passed: 53</t>
+          <t>Passed: 52</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Failed: 5</t>
+          <t>Failed: 6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Pass Percentage: 91.38%</t>
+          <t>Pass Percentage: 89.66%</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>16.53</v>
+        <v>16.56</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>15.7</v>
+        <v>15.58</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>11.47</v>
+        <v>11.44</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>12.25</v>
+        <v>12.22</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4.17</v>
+        <v>4.11</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
@@ -1262,17 +1262,18 @@
           <t>Profile Loads</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>3.11</v>
+        <v>3.02</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Executed Successfully</t>
+          <t>assert 'Profile Management' in '&lt;html lang="en"&gt;&lt;head&gt;\n    &lt;script type="module"&gt;import { injectIntoGlobalHook } from "/@react-refresh";\ninjectIntoGlobalHook(window);\nwindow.$RefreshReg$ = () =&gt; {};\nwindow.$RefreshSig$ = () =&gt; (type) =&gt; type;&lt;/script&gt;\n\n    &lt;script type="module" src="/@vite/client"&gt;&lt;/script&gt;\n\n    &lt;meta charset="UTF-8"&gt;\n    &lt;link rel="icon" type="image/svg+xml" href="data:image/svg+xml,&amp;lt;svg xmlns=%22http://www.w3.org/2000/svg%22 viewBox=%220%22 width=%22100%22 height=%22100%22&amp;gt;&amp;lt;text y=%220.9em%22 font-size=%2290%22&amp;gt;🧠&amp;lt;/text&amp;gt;&amp;lt;/svg&amp;gt;"&gt;\n    &lt;meta name="viewport" content="width=device-width, initial-scale=1.0"&gt;\n    &lt;title&gt;Neuro-Behavioral Drift | Cognitive Strain Monitor&lt;/title&gt;\n    &lt;!-- Google Fonts --&gt;\n    &lt;link rel="preconnect" href="https://fonts.googleapis.com"&gt;\n    &lt;link rel="preconnect" href="https://fonts.gstatic.com" crossorigin=""&gt;\n    &lt;link href="https://fonts.googleapis.com/css2?family=Outfit:wght@300;400;500;600;700;800&amp;amp;family=Inter:wght@300;400;500;600;700&amp;amp;display=swap" rel="stylesheet"&gt;\n  &lt;style type="text/css" data-vite-dev-id="/home/runner/work/neuro-behavioral-drift/neuro-behavioral-drift/frontend/src/index.css"&gt;*, ::before, ::after {\n..." class="lucide lucide-bell h-5 w-5"&gt;&lt;path d="M6 8a6 6 0 0 1 12 0c0 7 3 9 3 9H3s3-2 3-9"&gt;&lt;/path&gt;&lt;path d="M10.3 21a1.94 1.94 0 0 0 3.4 0"&gt;&lt;/path&gt;&lt;/svg&gt;&lt;/a&gt;&lt;a class="flex items-center gap-2 bg-slate-900 border border-slate-800/80 rounded-xl px-3 py-1.5 text-xs font-medium text-slate-300 hover:text-white hover:border-slate-700 transition-colors" href="/profile"&gt;&lt;svg xmlns="http://www.w3.org/2000/svg" width="24" height="24" viewBox="0 0 24 24" fill="none" stroke="currentColor" stroke-width="2" stroke-linecap="round" stroke-linejoin="round" class="lucide lucide-user h-3.5 w-3.5 text-accentBlue"&gt;&lt;path d="M19 21v-2a4 4 0 0 0-4-4H9a4 4 0 0 0-4 4v2"&gt;&lt;/path&gt;&lt;circle cx="12" cy="7" r="4"&gt;&lt;/circle&gt;&lt;/svg&gt;&lt;span&gt;Test User&lt;/span&gt;&lt;/a&gt;&lt;/div&gt;&lt;/div&gt;&lt;/header&gt;&lt;main class="flex-grow w-full"&gt;&lt;div class="flex justify-center items-center h-64 text-slate-400"&gt;Loading Profile...&lt;/div&gt;&lt;/main&gt;&lt;footer class="border-t border-slate-900 bg-slate-950/20 py-4 text-center text-xs text-slate-600"&gt;&lt;div class="container mx-auto"&gt;© 2026 Neuro-Behavioral Drift Modeling Platform. Local secure processing sandbox active.&lt;/div&gt;&lt;/footer&gt;&lt;/div&gt;&lt;/div&gt;\n    &lt;script type="module" src="/src/main.jsx"&gt;&lt;/script&gt;\n  \n\n&lt;/body&gt;&lt;/html&gt;'
+ +  where '&lt;html lang="en"&gt;&lt;head&gt;\n    &lt;script type="module"&gt;import { injectIntoGlobalHook } from "/@react-refresh";\ninjectIntoGlobalHook(window);\nwindow.$RefreshReg$ = () =&gt; {};\nwindow.$RefreshSig$ = () =&gt; (type) =&gt; type;&lt;/script&gt;\n\n    &lt;script type="module" src="/@vite/client"&gt;&lt;/script&gt;\n\n    &lt;meta charset="UTF-8"&gt;\n    &lt;link rel="icon" type="image/svg+xml" href="data:image/svg+xml,&amp;lt;svg xmlns=%22http://www.w3.org/2000/svg%22 viewBox=%220%22 width=%22100%22 height=%22100%22&amp;gt;&amp;lt;text y=%220.9em%22 font-size=%2290%22&amp;gt;🧠&amp;lt;/text&amp;gt;&amp;lt;/svg&amp;gt;"&gt;\n    &lt;meta name="viewport" content="width=device-width, initial-scale=1.0"&gt;\n    &lt;title&gt;Neuro-Behavioral Drift | Cognitive Strain Monitor&lt;/title&gt;\n    &lt;!-- Google Fonts --&gt;\n    &lt;link rel="preconnect" href="https://fonts.googleapis.com"&gt;\n    &lt;link rel="preconnect" href="https://fonts.gstatic.com" crossorigin=""&gt;\n    &lt;link href="https://fonts.googleapis.com/css2?family=Outfit:wght@300;400;500;600;700;800&amp;amp;family=Inter:wght@300;400;500;600;700&amp;amp;display=swap" rel="stylesheet"&gt;\n  &lt;style type="text/css" data-vite-dev-id="/home/runner/work/neuro-behavioral-drift/neuro-behavioral-drift/frontend/src/index.css"&gt;*, ::before, ::after {\n..." class="lucide lucide-bell h-5 w-5"&gt;&lt;path d="M6 8a6 6 0 0 1 12 0c0 7 3 9 3 9H3s3-2 3-9"&gt;&lt;/path&gt;&lt;path d="M10.3 21a1.94 1.94 0 0 0 3.4 0"&gt;&lt;/path&gt;&lt;/svg&gt;&lt;/a&gt;&lt;a class="flex items-center gap-2 bg-slate-900 border border-slate-800/80 rounded-xl px-3 py-1.5 text-xs font-medium text-slate-300 hover:text-white hover:border-slate-700 transition-colors" href="/profile"&gt;&lt;svg xmlns="http://www.w3.org/2000/svg" width="24" height="24" viewBox="0 0 24 24" fill="none" stroke="currentColor" stroke-width="2" stroke-linecap="round" stroke-linejoin="round" class="lucide lucide-user h-3.5 w-3.5 text-accentBlue"&gt;&lt;path d="M19 21v-2a4 4 0 0 0-4-4H9a4 4 0 0 0-4 4v2"&gt;&lt;/path&gt;&lt;circle cx="12" cy="7" r="4"&gt;&lt;/circle&gt;&lt;/svg&gt;&lt;span&gt;Test User&lt;/span&gt;&lt;/a&gt;&lt;/div&gt;&lt;/div&gt;&lt;/header&gt;&lt;main class="flex-grow w-full"&gt;&lt;div class="flex justify-center items-center h-64 text-slate-400"&gt;Loading Profile...&lt;/div&gt;&lt;/main&gt;&lt;footer class="border-t border-slate-900 bg-slate-950/20 py-4 text-center text-xs text-slate-600"&gt;&lt;div class="container mx-auto"&gt;© 2026 Neuro-Behavioral Drift Modeling Platform. Local secure processing sandbox active.&lt;/div&gt;&lt;/footer&gt;&lt;/div&gt;&lt;/div&gt;\n    &lt;script type="module" src="/src/main.jsx"&gt;&lt;/script&gt;\n  \n\n&lt;/body&gt;&lt;/html&gt;' = &lt;selenium.webdriver.chrome.webdriver.WebDriver (session="89473804dc02ff02337d94e78dd4fb18")&gt;.page_source</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1294,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>5.92</v>
+        <v>5.93</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
@@ -1318,7 +1319,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>4.09</v>
+        <v>4.05</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
@@ -1343,7 +1344,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
@@ -1368,7 +1369,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>4.31</v>
+        <v>4.3</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
@@ -1393,7 +1394,7 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -1418,7 +1419,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
@@ -1493,7 +1494,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
@@ -1518,7 +1519,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>5.2</v>
+        <v>5.38</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -1543,7 +1544,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
@@ -1568,7 +1569,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
@@ -1963,7 +1964,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
@@ -1988,7 +1989,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>

--- a/reports/Selenium_Test_Results.xlsx
+++ b/reports/Selenium_Test_Results.xlsx
@@ -478,7 +478,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Execution Date: 2026-06-20 13:18:32</t>
+          <t>Execution Date: 2026-06-21 06:41:21</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>5.34</v>
+        <v>5.32</v>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1.06</v>
+        <v>0.93</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1.43</v>
+        <v>1.12</v>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>6.02</v>
+        <v>6.04</v>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.25</v>
+        <v>0.18</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.19</v>
+        <v>0.09</v>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.25</v>
+        <v>0.43</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.02</v>
+        <v>0.52</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.52</v>
+        <v>0.02</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>0.52</v>
+        <v>0.02</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="G98" s="3" t="n">
-        <v>0.52</v>
+        <v>0.02</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="G123" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         </is>
       </c>
       <c r="G151" s="3" t="n">
-        <v>2.42</v>
+        <v>2.13</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="G152" s="3" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="G153" s="3" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="G154" s="3" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="G155" s="3" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="G156" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="G157" s="3" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="G158" s="3" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         </is>
       </c>
       <c r="G159" s="3" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         </is>
       </c>
       <c r="G160" s="3" t="n">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="G161" s="3" t="n">
-        <v>0.35</v>
+        <v>0.21</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         </is>
       </c>
       <c r="G163" s="3" t="n">
-        <v>2.14</v>
+        <v>2.61</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c r="G164" s="3" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="G165" s="3" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="G166" s="3" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="G167" s="3" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         </is>
       </c>
       <c r="G168" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         </is>
       </c>
       <c r="G169" s="3" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         </is>
       </c>
       <c r="G170" s="3" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         </is>
       </c>
       <c r="G171" s="3" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="G174" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         </is>
       </c>
       <c r="G176" s="3" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="G177" s="3" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="G179" s="3" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="G181" s="3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
         </is>
       </c>
       <c r="G182" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="G184" s="3" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         </is>
       </c>
       <c r="G187" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="G190" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="G198" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         </is>
       </c>
       <c r="G199" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         </is>
       </c>
       <c r="G201" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         </is>
       </c>
       <c r="G203" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         </is>
       </c>
       <c r="G204" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="G205" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         </is>
       </c>
       <c r="G207" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="G208" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         </is>
       </c>
       <c r="G218" s="3" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         </is>
       </c>
       <c r="G222" s="3" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="G241" s="3" t="n">
-        <v>0.28</v>
+        <v>0.11</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         </is>
       </c>
       <c r="G242" s="3" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         </is>
       </c>
       <c r="G251" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         </is>
       </c>
       <c r="G253" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         </is>
       </c>
       <c r="G261" s="3" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         </is>
       </c>
       <c r="G277" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H277" s="4" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="G287" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H287" s="4" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         </is>
       </c>
       <c r="G289" s="3" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H289" s="4" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         </is>
       </c>
       <c r="G290" s="3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H290" s="4" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="G297" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H297" s="4" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         </is>
       </c>
       <c r="G299" s="3" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H299" s="4" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         </is>
       </c>
       <c r="G301" s="3" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="H301" s="4" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         </is>
       </c>
       <c r="G302" s="3" t="n">
-        <v>0.44</v>
+        <v>0.27</v>
       </c>
       <c r="H302" s="4" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         </is>
       </c>
       <c r="G303" s="3" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="H303" s="4" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         </is>
       </c>
       <c r="G304" s="3" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         </is>
       </c>
       <c r="G305" s="3" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="H305" s="4" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         </is>
       </c>
       <c r="G306" s="3" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="H306" s="4" t="inlineStr">
         <is>
@@ -12471,7 +12471,7 @@
         </is>
       </c>
       <c r="G307" s="3" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="H307" s="4" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         </is>
       </c>
       <c r="G308" s="3" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="H308" s="4" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         </is>
       </c>
       <c r="G310" s="3" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="G311" s="3" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="H311" s="4" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         </is>
       </c>
       <c r="G312" s="3" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="H312" s="4" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         </is>
       </c>
       <c r="G314" s="3" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="H314" s="4" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         </is>
       </c>
       <c r="G316" s="3" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="H316" s="4" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         </is>
       </c>
       <c r="G317" s="3" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         </is>
       </c>
       <c r="G319" s="3" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="H319" s="4" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         </is>
       </c>
       <c r="G320" s="3" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="H320" s="4" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="G323" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H323" s="4" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         </is>
       </c>
       <c r="G326" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H326" s="4" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         </is>
       </c>
       <c r="G327" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H327" s="4" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         </is>
       </c>
       <c r="G328" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H328" s="4" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         </is>
       </c>
       <c r="G330" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H330" s="4" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         </is>
       </c>
       <c r="G331" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H331" s="4" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         </is>
       </c>
       <c r="G333" s="3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="H333" s="4" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         </is>
       </c>
       <c r="G334" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H334" s="4" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         </is>
       </c>
       <c r="G336" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H336" s="4" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         </is>
       </c>
       <c r="G337" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H337" s="4" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         </is>
       </c>
       <c r="G342" s="3" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="H342" s="4" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         </is>
       </c>
       <c r="G343" s="3" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="H343" s="4" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         </is>
       </c>
       <c r="G345" s="3" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="H345" s="4" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         </is>
       </c>
       <c r="G346" s="3" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="H346" s="4" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="G348" s="3" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="H348" s="4" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         </is>
       </c>
       <c r="G349" s="3" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="H349" s="4" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         </is>
       </c>
       <c r="G350" s="3" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="H350" s="4" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         </is>
       </c>
       <c r="G351" s="3" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="H351" s="4" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         </is>
       </c>
       <c r="G352" s="3" t="n">
-        <v>0.38</v>
+        <v>0.29</v>
       </c>
       <c r="H352" s="4" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="G353" s="3" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="H353" s="4" t="inlineStr">
         <is>
@@ -14351,7 +14351,7 @@
         </is>
       </c>
       <c r="G354" s="3" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="H354" s="4" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         </is>
       </c>
       <c r="G355" s="3" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="H355" s="4" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         </is>
       </c>
       <c r="G356" s="3" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="H356" s="4" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         </is>
       </c>
       <c r="G357" s="3" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="H357" s="4" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         </is>
       </c>
       <c r="G359" s="3" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="H359" s="4" t="inlineStr">
         <is>
@@ -14591,7 +14591,7 @@
         </is>
       </c>
       <c r="G360" s="3" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="H360" s="4" t="inlineStr">
         <is>
